--- a/Plotting/Results_excels/result_data_long_LowAmbition.xlsx
+++ b/Plotting/Results_excels/result_data_long_LowAmbition.xlsx
@@ -559,32 +559,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20250907_05_27\Iteration_1\20250907090852_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20251119_08_51\Iteration_1\20251119142446_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20250907_05_27\Iteration_1\20250907095857_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20251119_08_51\Iteration_1\20251119151149_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20250907_05_27\Iteration_1\20250907110653_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20251119_08_51\Iteration_1\20251119162932_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20250907_05_27\Iteration_2\20250907150444_2030_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20251119_08_51\Iteration_2\20251119211323_2030_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20250907_05_27\Iteration_2\20250907155041_2040_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20251119_08_51\Iteration_2\20251119215837_2040_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20250907_05_27\Iteration_2\20250907165307_2050_minC_DD10-1\optimization_results.h5</t>
+          <t>Z:\AdOpt_NET0\AdOpt_results\Model_Linking\Full\LowAmbition\Results_model_linking_20251119_08_51\Iteration_2\20251119230421_2050_minC_DD10-1\optimization_results.h5</t>
         </is>
       </c>
     </row>
@@ -604,22 +604,22 @@
         <v>1012908906.929864</v>
       </c>
       <c r="E5" t="n">
-        <v>2691585006.760958</v>
+        <v>2690115637.20856</v>
       </c>
       <c r="F5" t="n">
-        <v>1609617107.365047</v>
+        <v>1602985796.157647</v>
       </c>
       <c r="G5" t="n">
-        <v>1051046531.092047</v>
+        <v>1048762287.47741</v>
       </c>
       <c r="H5" t="n">
-        <v>2697683164.420156</v>
+        <v>2689960935.704401</v>
       </c>
       <c r="I5" t="n">
-        <v>1604686996.576777</v>
+        <v>1605220485.602691</v>
       </c>
       <c r="J5" t="n">
-        <v>1051913105.41045</v>
+        <v>1045540437.929909</v>
       </c>
     </row>
     <row r="6">
@@ -637,17 +637,17 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>404047658.3859068</v>
+        <v>404047783.4100429</v>
       </c>
       <c r="G6" t="n">
-        <v>493594145.4871573</v>
+        <v>493920946.1855053</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>404047658.3749291</v>
+        <v>404047658.3810866</v>
       </c>
       <c r="J6" t="n">
-        <v>490957243.8495642</v>
+        <v>493944297.4278492</v>
       </c>
     </row>
     <row r="7">
@@ -666,22 +666,22 @@
         <v>1409097582.297616</v>
       </c>
       <c r="E7" t="n">
-        <v>2691585006.760958</v>
+        <v>2690115637.20856</v>
       </c>
       <c r="F7" t="n">
-        <v>2013664765.750954</v>
+        <v>2007033579.56769</v>
       </c>
       <c r="G7" t="n">
-        <v>1544640676.579204</v>
+        <v>1542683233.662915</v>
       </c>
       <c r="H7" t="n">
-        <v>2697683164.420156</v>
+        <v>2689960935.704401</v>
       </c>
       <c r="I7" t="n">
-        <v>2008734654.951706</v>
+        <v>2009268143.983778</v>
       </c>
       <c r="J7" t="n">
-        <v>1542870349.260014</v>
+        <v>1539484735.357758</v>
       </c>
     </row>
     <row r="8">
@@ -698,12 +698,12 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>58458427907.05209</v>
+        <v>58357846670.29122</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>58452405102.56947</v>
+        <v>58346661566.6485</v>
       </c>
     </row>
     <row r="9">
@@ -722,22 +722,22 @@
         <v>80970.60823717949</v>
       </c>
       <c r="E9" t="n">
-        <v>1065926.393684468</v>
+        <v>1091209.079867617</v>
       </c>
       <c r="F9" t="n">
-        <v>77557.83691849151</v>
+        <v>81831.82267069934</v>
       </c>
       <c r="G9" t="n">
-        <v>36098.32453859237</v>
+        <v>36101.70906148446</v>
       </c>
       <c r="H9" t="n">
-        <v>1075791.704510676</v>
+        <v>1070466.495734658</v>
       </c>
       <c r="I9" t="n">
-        <v>80166.12979556307</v>
+        <v>80471.30831350198</v>
       </c>
       <c r="J9" t="n">
-        <v>37762.82149309024</v>
+        <v>37748.36763767673</v>
       </c>
     </row>
     <row r="10">
@@ -756,22 +756,22 @@
         <v>8671074.289434575</v>
       </c>
       <c r="E10" t="n">
-        <v>404047658.3859068</v>
+        <v>404047783.4100429</v>
       </c>
       <c r="F10" t="n">
-        <v>89546487.1012505</v>
+        <v>89873162.77546237</v>
       </c>
       <c r="G10" t="n">
-        <v>2506589.476088839</v>
+        <v>-1.380148849140447e-11</v>
       </c>
       <c r="H10" t="n">
-        <v>404047658.3749291</v>
+        <v>404047658.3810866</v>
       </c>
       <c r="I10" t="n">
-        <v>86909585.47463514</v>
+        <v>89896639.04676266</v>
       </c>
       <c r="J10" t="n">
-        <v>0.01209461247518446</v>
+        <v>27663.55753778234</v>
       </c>
     </row>
     <row r="11">
@@ -790,22 +790,22 @@
         <v>222642991.4889718</v>
       </c>
       <c r="E11" t="n">
-        <v>276718309.6226121</v>
+        <v>276718363.005335</v>
       </c>
       <c r="F11" t="n">
-        <v>219333178.4894906</v>
+        <v>219480834.0254743</v>
       </c>
       <c r="G11" t="n">
-        <v>207590609.7247264</v>
+        <v>206587265.0014755</v>
       </c>
       <c r="H11" t="n">
-        <v>276718309.6224749</v>
+        <v>276718309.6225886</v>
       </c>
       <c r="I11" t="n">
-        <v>218630086.9148192</v>
+        <v>219468429.8249123</v>
       </c>
       <c r="J11" t="n">
-        <v>205736517.8908191</v>
+        <v>206592578.93803</v>
       </c>
     </row>
     <row r="12">
@@ -824,22 +824,22 @@
         <v>769279211.6385828</v>
       </c>
       <c r="E12" t="n">
-        <v>1848691634.273031</v>
+        <v>1843376589.745317</v>
       </c>
       <c r="F12" t="n">
-        <v>1288940894.779003</v>
+        <v>1281185179.128497</v>
       </c>
       <c r="G12" t="n">
-        <v>835458776.7289118</v>
+        <v>836683952.5276831</v>
       </c>
       <c r="H12" t="n">
-        <v>1853289278.166675</v>
+        <v>1846377013.699484</v>
       </c>
       <c r="I12" t="n">
-        <v>1286954055.845417</v>
+        <v>1283615730.736532</v>
       </c>
       <c r="J12" t="n">
-        <v>840432862.3584371</v>
+        <v>833178668.7166504</v>
       </c>
     </row>
     <row r="13">
@@ -858,22 +858,22 @@
         <v>12315629.5128746</v>
       </c>
       <c r="E13" t="n">
-        <v>162127404.4794086</v>
+        <v>165972901.0478654</v>
       </c>
       <c r="F13" t="n">
-        <v>11796546.99530255</v>
+        <v>12446620.22821337</v>
       </c>
       <c r="G13" t="n">
-        <v>5490555.1623199</v>
+        <v>5491069.948250866</v>
       </c>
       <c r="H13" t="n">
-        <v>163627918.2560768</v>
+        <v>162817954.0012427</v>
       </c>
       <c r="I13" t="n">
-        <v>12193268.34190515</v>
+        <v>12239685.99448366</v>
       </c>
       <c r="J13" t="n">
-        <v>5743725.149099028</v>
+        <v>5741526.717690633</v>
       </c>
     </row>
     <row r="14">
@@ -929,7 +929,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>32.00868314699161</v>
+        <v>31.8795469581674</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>31.51539294185948</v>
+        <v>31.87882565555898</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>628.7238300898948</v>
+        <v>628.7238300899735</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>628.7238300921241</v>
+        <v>628.7238300901352</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>676.5329554230281</v>
+        <v>676.5455850097911</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1071,7 +1071,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>676.5329554223388</v>
+        <v>676.5329554229265</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1324,7 +1324,7 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4012.320629269281</v>
+        <v>4012.320629268933</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4012.320629265319</v>
+        <v>4012.320629268594</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>921.1131840860896</v>
+        <v>917.397034767407</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>906.9177824995534</v>
+        <v>917.3762778578124</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>617.5001571651119</v>
+        <v>617.500157165118</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1537,7 +1537,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>617.5001571642975</v>
+        <v>617.5001571650524</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>750.3039576734022</v>
+        <v>750.3039576732568</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1571,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>750.3039576726834</v>
+        <v>750.3039576732388</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -1676,22 +1676,22 @@
         <v>0.1163839023097688</v>
       </c>
       <c r="E39" t="n">
-        <v>123.6218069560984</v>
+        <v>123.6459097831228</v>
       </c>
       <c r="F39" t="n">
-        <v>4.244335202231336</v>
+        <v>4.316628828173946</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>123.508632728054</v>
+        <v>123.5710424813264</v>
       </c>
       <c r="I39" t="n">
-        <v>3.933245327369641</v>
+        <v>4.455853689823497</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1291072812603055</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1885,19 +1885,19 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>2740.040116460392</v>
+        <v>4652.927583227691</v>
       </c>
       <c r="G46" t="n">
-        <v>1451.298418758104</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>3729.236732011574</v>
+        <v>4347.406267900969</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>283.6717438001624</v>
       </c>
     </row>
     <row r="47">
@@ -1925,10 +1925,10 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>9.675369009124017e-10</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>15.36860572881631</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -1953,16 +1953,16 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>185.4839275243623</v>
+        <v>184.7356090954777</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>4.159533518728575e-10</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>182.6254092829967</v>
+        <v>187.8261948428381</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>5756.853584693607</v>
+        <v>5756.866214279549</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>5756.853584687658</v>
+        <v>5756.85358469152</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>750.3039576733556</v>
+        <v>750.3039576732905</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>750.3039576729495</v>
+        <v>750.3039576732108</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
@@ -2120,19 +2120,19 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>71.47200000059345</v>
+        <v>71.47200000127492</v>
       </c>
       <c r="F53" t="n">
-        <v>106.7661899436962</v>
+        <v>51.82831382283925</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>71.4720002164818</v>
+        <v>71.47200000204134</v>
       </c>
       <c r="I53" t="n">
-        <v>49.55562862510408</v>
+        <v>51.82381217354123</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2460,22 +2460,22 @@
         <v>128.3166308989123</v>
       </c>
       <c r="E63" t="n">
-        <v>123.6218069560984</v>
+        <v>123.6459097831228</v>
       </c>
       <c r="F63" t="n">
-        <v>127.8661421583298</v>
+        <v>127.9625386113154</v>
       </c>
       <c r="G63" t="n">
-        <v>127.8661421583447</v>
+        <v>127.9625386112967</v>
       </c>
       <c r="H63" t="n">
-        <v>123.508632728054</v>
+        <v>123.5710424813264</v>
       </c>
       <c r="I63" t="n">
-        <v>127.4418780554469</v>
+        <v>128.0268961711499</v>
       </c>
       <c r="J63" t="n">
-        <v>127.5709853366839</v>
+        <v>128.0268961711545</v>
       </c>
     </row>
     <row r="64">
@@ -2528,22 +2528,22 @@
         <v>137.0524669588513</v>
       </c>
       <c r="E65" t="n">
-        <v>136.5416640003214</v>
+        <v>136.5416640004932</v>
       </c>
       <c r="F65" t="n">
-        <v>154.7470149264631</v>
+        <v>154.1227018409244</v>
       </c>
       <c r="G65" t="n">
-        <v>154.7470149264631</v>
+        <v>154.1227018409244</v>
       </c>
       <c r="H65" t="n">
-        <v>136.5416640011849</v>
+        <v>136.541664000502</v>
       </c>
       <c r="I65" t="n">
-        <v>152.362187459925</v>
+        <v>154.1192146801125</v>
       </c>
       <c r="J65" t="n">
-        <v>152.3621874599253</v>
+        <v>154.1192146801125</v>
       </c>
     </row>
     <row r="66">
@@ -2701,19 +2701,19 @@
         <v>1900</v>
       </c>
       <c r="F70" t="n">
-        <v>3067.322420412919</v>
+        <v>3069.296962062781</v>
       </c>
       <c r="G70" t="n">
-        <v>3096.158566930568</v>
+        <v>3069.814124496264</v>
       </c>
       <c r="H70" t="n">
-        <v>1900.000000055451</v>
+        <v>1900</v>
       </c>
       <c r="I70" t="n">
-        <v>3033.884381935132</v>
+        <v>3069.733463423367</v>
       </c>
       <c r="J70" t="n">
-        <v>3034.692867581616</v>
+        <v>3078.306632658481</v>
       </c>
     </row>
     <row r="71">
@@ -2868,22 +2868,22 @@
         <v>89.06934219303602</v>
       </c>
       <c r="E75" t="n">
-        <v>78.91824459420788</v>
+        <v>78.89414176736361</v>
       </c>
       <c r="F75" t="n">
-        <v>113.0374940389406</v>
+        <v>113.0712098588004</v>
       </c>
       <c r="G75" t="n">
-        <v>123.3332804807715</v>
+        <v>141.4433130132693</v>
       </c>
       <c r="H75" t="n">
-        <v>79.03141887636799</v>
+        <v>78.96900906910189</v>
       </c>
       <c r="I75" t="n">
-        <v>111.7348503675771</v>
+        <v>113.8471222132658</v>
       </c>
       <c r="J75" t="n">
-        <v>111.6057430862973</v>
+        <v>141.2136819544899</v>
       </c>
     </row>
     <row r="76">
@@ -3038,22 +3038,22 @@
         <v>3466.008304390369</v>
       </c>
       <c r="E80" t="n">
-        <v>5756.853584693784</v>
+        <v>5756.866214279549</v>
       </c>
       <c r="F80" t="n">
-        <v>4012.320629269281</v>
+        <v>4012.320629269021</v>
       </c>
       <c r="G80" t="n">
-        <v>4012.320629269321</v>
+        <v>4012.320629268947</v>
       </c>
       <c r="H80" t="n">
-        <v>5756.853584693136</v>
+        <v>5756.85358469583</v>
       </c>
       <c r="I80" t="n">
-        <v>4012.320629265319</v>
+        <v>4012.320629268665</v>
       </c>
       <c r="J80" t="n">
-        <v>4012.320629265331</v>
+        <v>4012.320629268653</v>
       </c>
     </row>
     <row r="81">
@@ -3415,19 +3415,19 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>9.08745348240673</v>
+        <v>9.190762433466091</v>
       </c>
       <c r="G91" t="n">
-        <v>9.087453482406758</v>
+        <v>9.190762433466091</v>
       </c>
       <c r="H91" t="n">
-        <v>5.590500156016091e-10</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>9.482085646512417</v>
+        <v>9.191339475552809</v>
       </c>
       <c r="J91" t="n">
-        <v>9.482085646512459</v>
+        <v>9.191339475552837</v>
       </c>
     </row>
     <row r="92">
@@ -3853,17 +3853,17 @@
       </c>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="n">
-        <v>628.7238300898948</v>
+        <v>628.7238300899735</v>
       </c>
       <c r="G104" t="n">
-        <v>628.7238300898948</v>
+        <v>628.7238300899735</v>
       </c>
       <c r="H104" t="inlineStr"/>
       <c r="I104" t="n">
-        <v>628.7238300921241</v>
+        <v>628.7238300901352</v>
       </c>
       <c r="J104" t="n">
-        <v>628.7238300921241</v>
+        <v>628.7238300901352</v>
       </c>
     </row>
     <row r="105">
@@ -3881,17 +3881,17 @@
       </c>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>676.5329554230281</v>
+        <v>676.5455850097911</v>
       </c>
       <c r="G105" t="n">
-        <v>676.5329554230281</v>
+        <v>676.5455850097911</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="n">
-        <v>676.5329554223388</v>
+        <v>676.5329554229265</v>
       </c>
       <c r="J105" t="n">
-        <v>676.5329554223388</v>
+        <v>676.5329554229265</v>
       </c>
     </row>
     <row r="106">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="E106" t="inlineStr"/>
       <c r="F106" t="n">
-        <v>108.6165055439348</v>
+        <v>108.8322687169892</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="n">
-        <v>105.7528010414205</v>
+        <v>108.8403222131715</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -3965,17 +3965,17 @@
       </c>
       <c r="E108" t="inlineStr"/>
       <c r="F108" t="n">
-        <v>123.6218069560984</v>
+        <v>123.6459097831228</v>
       </c>
       <c r="G108" t="n">
-        <v>127.8661421583298</v>
+        <v>127.9625386112967</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="n">
-        <v>123.508632728054</v>
+        <v>123.5710424813264</v>
       </c>
       <c r="J108" t="n">
-        <v>127.4418780554236</v>
+        <v>128.0268961711498</v>
       </c>
     </row>
     <row r="109">
@@ -3993,17 +3993,17 @@
       </c>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="n">
-        <v>5756.853584693607</v>
+        <v>5756.866214279549</v>
       </c>
       <c r="G109" t="n">
-        <v>5756.853584693607</v>
+        <v>5756.866214279549</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="n">
-        <v>5756.853584687658</v>
+        <v>5756.85358469152</v>
       </c>
       <c r="J109" t="n">
-        <v>5756.853584687658</v>
+        <v>5756.85358469152</v>
       </c>
     </row>
     <row r="110">
@@ -4020,12 +4020,12 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>32.00868314699161</v>
+        <v>31.8795469581674</v>
       </c>
       <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="n">
-        <v>31.51539294185948</v>
+        <v>31.87882565555898</v>
       </c>
     </row>
     <row r="111">
@@ -4060,12 +4060,12 @@
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>108.6165055439348</v>
+        <v>108.8322687169892</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="n">
-        <v>105.7528010414205</v>
+        <v>108.8403222131715</v>
       </c>
     </row>
     <row r="113">
@@ -4081,17 +4081,17 @@
       </c>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="n">
-        <v>4012.320629269281</v>
+        <v>4012.320629268933</v>
       </c>
       <c r="G113" t="n">
-        <v>4012.320629269281</v>
+        <v>4012.320629268933</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="n">
-        <v>4012.320629265319</v>
+        <v>4012.320629268594</v>
       </c>
       <c r="J113" t="n">
-        <v>4012.320629265319</v>
+        <v>4012.320629268594</v>
       </c>
     </row>
     <row r="114">
@@ -4108,12 +4108,12 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>921.1131840860896</v>
+        <v>917.397034767407</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="n">
-        <v>906.9177824995534</v>
+        <v>917.3762778578124</v>
       </c>
     </row>
     <row r="115">
@@ -4129,17 +4129,17 @@
       </c>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="n">
-        <v>617.5001571651119</v>
+        <v>617.500157165118</v>
       </c>
       <c r="G115" t="n">
-        <v>617.5001571651119</v>
+        <v>617.500157165118</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="n">
-        <v>617.5001571642975</v>
+        <v>617.5001571650524</v>
       </c>
       <c r="J115" t="n">
-        <v>617.5001571642975</v>
+        <v>617.5001571650524</v>
       </c>
     </row>
     <row r="116">
@@ -4155,17 +4155,17 @@
       </c>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="n">
-        <v>750.3039576734022</v>
+        <v>750.3039576732568</v>
       </c>
       <c r="G116" t="n">
-        <v>750.3039576734022</v>
+        <v>750.3039576732568</v>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="n">
-        <v>750.3039576726834</v>
+        <v>750.3039576732388</v>
       </c>
       <c r="J116" t="n">
-        <v>750.3039576726834</v>
+        <v>750.3039576732388</v>
       </c>
     </row>
     <row r="117">
@@ -4182,12 +4182,12 @@
       <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="n">
-        <v>2740.040116460392</v>
+        <v>4652.927583227691</v>
       </c>
       <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="n">
-        <v>3729.236732011574</v>
+        <v>4347.406267900969</v>
       </c>
     </row>
     <row r="118">
@@ -4203,17 +4203,17 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="n">
-        <v>750.3039576733556</v>
+        <v>750.3039576732905</v>
       </c>
       <c r="G118" t="n">
-        <v>750.3039576733556</v>
+        <v>750.3039576732905</v>
       </c>
       <c r="H118" t="inlineStr"/>
       <c r="I118" t="n">
-        <v>750.3039576729495</v>
+        <v>750.3039576732108</v>
       </c>
       <c r="J118" t="n">
-        <v>750.3039576729495</v>
+        <v>750.3039576732108</v>
       </c>
     </row>
     <row r="119">
@@ -4228,14 +4228,12 @@
       <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="n">
-        <v>185.4839275243623</v>
+        <v>184.7356090954777</v>
       </c>
       <c r="H119" t="inlineStr"/>
-      <c r="I119" t="n">
-        <v>4.159533518728575e-10</v>
-      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="n">
-        <v>182.6254092834127</v>
+        <v>187.8261948428381</v>
       </c>
     </row>
     <row r="120">
@@ -4251,11 +4249,9 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr"/>
-      <c r="I120" t="n">
-        <v>9.675369009124017e-10</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="J120" t="n">
-        <v>9.675369009124017e-10</v>
+        <v>15.36860572881631</v>
       </c>
     </row>
   </sheetData>
